--- a/artfynd/A 4226-2026 artfynd.xlsx
+++ b/artfynd/A 4226-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -809,45 +809,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131428209</v>
+        <v>136663274</v>
       </c>
       <c r="B3" t="n">
-        <v>91433</v>
+        <v>89332</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>233196</v>
+        <v>4412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällfotad fingersvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramaria rufescens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Corner</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Backvallen, Jmt</t>
+          <t>Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>485502</v>
+        <v>485464</v>
       </c>
       <c r="R3" t="n">
-        <v>6991022</v>
+        <v>6990942</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,17 +874,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-09-01</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-09-01</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>kalkbarrskog</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +904,2296 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136663274</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136663296</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93426</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Backvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>485408</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6990984</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136663296</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136663269</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91614</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5747</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>485500</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6991043</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136663269</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136663273</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91614</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5747</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>485434</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6991000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136663273</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136663272</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91622</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5754</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gultoppig fingersvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ramaria testaceoflava</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>485396</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6990976</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136663272</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136663265</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93436</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>485489</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6990968</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136663265</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136663297</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93436</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Backvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>485524</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6990966</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136663297</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136663259</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79474</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>485412</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6991015</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136663259</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136663254</v>
+      </c>
+      <c r="B11" t="n">
+        <v>102468</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>485478</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6991039</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>i kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136663254</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136663318</v>
+      </c>
+      <c r="B12" t="n">
+        <v>102468</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Backvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>485486</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6991039</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>i kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136663318</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136663327</v>
+      </c>
+      <c r="B13" t="n">
+        <v>102468</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Backvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>485496</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6991024</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>i kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136663327</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136663306</v>
+      </c>
+      <c r="B14" t="n">
+        <v>103917</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Backvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>485489</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6990981</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>i kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136663306</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136663313</v>
+      </c>
+      <c r="B15" t="n">
+        <v>103917</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Backvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>485476</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6991002</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>i kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136663313</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136663331</v>
+      </c>
+      <c r="B16" t="n">
+        <v>103917</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Backvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>485522</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6990976</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136663331</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136663248</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98358</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222741</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Finbräken</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Cystopteris montana</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>485409</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6990991</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>i kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136663248</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136663250</v>
+      </c>
+      <c r="B18" t="n">
+        <v>101454</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>485349</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6990987</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>i kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136663250</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136663257</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101454</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>485482</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6991029</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>i kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136663257</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136663308</v>
+      </c>
+      <c r="B20" t="n">
+        <v>101454</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Backvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>485416</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6991007</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>i kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136663308</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136663324</v>
+      </c>
+      <c r="B21" t="n">
+        <v>101454</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Backvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>485471</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6991009</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>i kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136663324</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136663325</v>
+      </c>
+      <c r="B22" t="n">
+        <v>101454</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Backvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>485498</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6991013</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>i kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136663325</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136663264</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79662</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>230552</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gropig skägglav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Usnea barbata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>485473</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6991060</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136663264</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>131428209</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91433</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>233196</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Fjällfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Ramaria rufescens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Corner</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Backvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>485502</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6991022</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2017-09-01</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2017-09-01</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
           <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
+      <c r="AZ24" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/131428209</t>
         </is>
@@ -922,6 +3203,27 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4226-2026 artfynd.xlsx
+++ b/artfynd/A 4226-2026 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>136663274</v>
       </c>
       <c r="B3" t="n">
-        <v>89332</v>
+        <v>89334</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>136663296</v>
       </c>
       <c r="B4" t="n">
-        <v>93426</v>
+        <v>93429</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136663269</v>
       </c>
       <c r="B5" t="n">
-        <v>91614</v>
+        <v>91616</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>136663273</v>
       </c>
       <c r="B6" t="n">
-        <v>91614</v>
+        <v>91616</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>136663272</v>
       </c>
       <c r="B7" t="n">
-        <v>91622</v>
+        <v>91624</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>136663265</v>
       </c>
       <c r="B8" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>136663297</v>
       </c>
       <c r="B9" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>136663254</v>
       </c>
       <c r="B11" t="n">
-        <v>102468</v>
+        <v>102471</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>136663318</v>
       </c>
       <c r="B12" t="n">
-        <v>102468</v>
+        <v>102471</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>136663327</v>
       </c>
       <c r="B13" t="n">
-        <v>102468</v>
+        <v>102471</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>136663306</v>
       </c>
       <c r="B14" t="n">
-        <v>103917</v>
+        <v>103920</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>136663313</v>
       </c>
       <c r="B15" t="n">
-        <v>103917</v>
+        <v>103920</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>136663331</v>
       </c>
       <c r="B16" t="n">
-        <v>103917</v>
+        <v>103920</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>136663248</v>
       </c>
       <c r="B17" t="n">
-        <v>98358</v>
+        <v>98361</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>136663250</v>
       </c>
       <c r="B18" t="n">
-        <v>101454</v>
+        <v>101457</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>136663257</v>
       </c>
       <c r="B19" t="n">
-        <v>101454</v>
+        <v>101457</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>136663308</v>
       </c>
       <c r="B20" t="n">
-        <v>101454</v>
+        <v>101457</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>136663324</v>
       </c>
       <c r="B21" t="n">
-        <v>101454</v>
+        <v>101457</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>136663325</v>
       </c>
       <c r="B22" t="n">
-        <v>101454</v>
+        <v>101457</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 4226-2026 artfynd.xlsx
+++ b/artfynd/A 4226-2026 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>136663296</v>
       </c>
       <c r="B4" t="n">
-        <v>93429</v>
+        <v>93430</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>136663265</v>
       </c>
       <c r="B8" t="n">
-        <v>93439</v>
+        <v>93440</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>136663297</v>
       </c>
       <c r="B9" t="n">
-        <v>93439</v>
+        <v>93440</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>136663254</v>
       </c>
       <c r="B11" t="n">
-        <v>102471</v>
+        <v>102472</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>136663318</v>
       </c>
       <c r="B12" t="n">
-        <v>102471</v>
+        <v>102472</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>136663327</v>
       </c>
       <c r="B13" t="n">
-        <v>102471</v>
+        <v>102472</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>136663306</v>
       </c>
       <c r="B14" t="n">
-        <v>103920</v>
+        <v>103921</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>136663313</v>
       </c>
       <c r="B15" t="n">
-        <v>103920</v>
+        <v>103921</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>136663331</v>
       </c>
       <c r="B16" t="n">
-        <v>103920</v>
+        <v>103921</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>136663248</v>
       </c>
       <c r="B17" t="n">
-        <v>98361</v>
+        <v>98362</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>136663250</v>
       </c>
       <c r="B18" t="n">
-        <v>101457</v>
+        <v>101458</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>136663257</v>
       </c>
       <c r="B19" t="n">
-        <v>101457</v>
+        <v>101458</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>136663308</v>
       </c>
       <c r="B20" t="n">
-        <v>101457</v>
+        <v>101458</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>136663324</v>
       </c>
       <c r="B21" t="n">
-        <v>101457</v>
+        <v>101458</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>136663325</v>
       </c>
       <c r="B22" t="n">
-        <v>101457</v>
+        <v>101458</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 4226-2026 artfynd.xlsx
+++ b/artfynd/A 4226-2026 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>136663274</v>
       </c>
       <c r="B3" t="n">
-        <v>89334</v>
+        <v>89336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>136663296</v>
       </c>
       <c r="B4" t="n">
-        <v>93430</v>
+        <v>93435</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136663269</v>
       </c>
       <c r="B5" t="n">
-        <v>91616</v>
+        <v>91618</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>136663273</v>
       </c>
       <c r="B6" t="n">
-        <v>91616</v>
+        <v>91618</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>136663272</v>
       </c>
       <c r="B7" t="n">
-        <v>91624</v>
+        <v>91626</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>136663265</v>
       </c>
       <c r="B8" t="n">
-        <v>93440</v>
+        <v>93445</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>136663297</v>
       </c>
       <c r="B9" t="n">
-        <v>93440</v>
+        <v>93445</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>136663259</v>
       </c>
       <c r="B10" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>136663254</v>
       </c>
       <c r="B11" t="n">
-        <v>102472</v>
+        <v>102477</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>136663318</v>
       </c>
       <c r="B12" t="n">
-        <v>102472</v>
+        <v>102477</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>136663327</v>
       </c>
       <c r="B13" t="n">
-        <v>102472</v>
+        <v>102477</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>136663306</v>
       </c>
       <c r="B14" t="n">
-        <v>103921</v>
+        <v>103926</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>136663313</v>
       </c>
       <c r="B15" t="n">
-        <v>103921</v>
+        <v>103926</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>136663331</v>
       </c>
       <c r="B16" t="n">
-        <v>103921</v>
+        <v>103926</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>136663248</v>
       </c>
       <c r="B17" t="n">
-        <v>98362</v>
+        <v>98367</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>136663250</v>
       </c>
       <c r="B18" t="n">
-        <v>101458</v>
+        <v>101463</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>136663257</v>
       </c>
       <c r="B19" t="n">
-        <v>101458</v>
+        <v>101463</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>136663308</v>
       </c>
       <c r="B20" t="n">
-        <v>101458</v>
+        <v>101463</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>136663324</v>
       </c>
       <c r="B21" t="n">
-        <v>101458</v>
+        <v>101463</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>136663325</v>
       </c>
       <c r="B22" t="n">
-        <v>101458</v>
+        <v>101463</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>136663264</v>
       </c>
       <c r="B23" t="n">
-        <v>79662</v>
+        <v>79664</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 4226-2026 artfynd.xlsx
+++ b/artfynd/A 4226-2026 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>136663274</v>
       </c>
       <c r="B3" t="n">
-        <v>89336</v>
+        <v>89338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>136663296</v>
       </c>
       <c r="B4" t="n">
-        <v>93435</v>
+        <v>93437</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136663269</v>
       </c>
       <c r="B5" t="n">
-        <v>91618</v>
+        <v>91620</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>136663273</v>
       </c>
       <c r="B6" t="n">
-        <v>91618</v>
+        <v>91620</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>136663272</v>
       </c>
       <c r="B7" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>136663265</v>
       </c>
       <c r="B8" t="n">
-        <v>93445</v>
+        <v>93447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>136663297</v>
       </c>
       <c r="B9" t="n">
-        <v>93445</v>
+        <v>93447</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>136663254</v>
       </c>
       <c r="B11" t="n">
-        <v>102477</v>
+        <v>102479</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>136663318</v>
       </c>
       <c r="B12" t="n">
-        <v>102477</v>
+        <v>102479</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>136663327</v>
       </c>
       <c r="B13" t="n">
-        <v>102477</v>
+        <v>102479</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>136663306</v>
       </c>
       <c r="B14" t="n">
-        <v>103926</v>
+        <v>103928</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>136663313</v>
       </c>
       <c r="B15" t="n">
-        <v>103926</v>
+        <v>103928</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>136663331</v>
       </c>
       <c r="B16" t="n">
-        <v>103926</v>
+        <v>103928</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>136663248</v>
       </c>
       <c r="B17" t="n">
-        <v>98367</v>
+        <v>98369</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>136663250</v>
       </c>
       <c r="B18" t="n">
-        <v>101463</v>
+        <v>101465</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>136663257</v>
       </c>
       <c r="B19" t="n">
-        <v>101463</v>
+        <v>101465</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>136663308</v>
       </c>
       <c r="B20" t="n">
-        <v>101463</v>
+        <v>101465</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>136663324</v>
       </c>
       <c r="B21" t="n">
-        <v>101463</v>
+        <v>101465</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>136663325</v>
       </c>
       <c r="B22" t="n">
-        <v>101463</v>
+        <v>101465</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 4226-2026 artfynd.xlsx
+++ b/artfynd/A 4226-2026 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>136663274</v>
       </c>
       <c r="B3" t="n">
-        <v>89338</v>
+        <v>89340</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>136663296</v>
       </c>
       <c r="B4" t="n">
-        <v>93437</v>
+        <v>93439</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136663269</v>
       </c>
       <c r="B5" t="n">
-        <v>91620</v>
+        <v>91622</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>136663273</v>
       </c>
       <c r="B6" t="n">
-        <v>91620</v>
+        <v>91622</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>136663272</v>
       </c>
       <c r="B7" t="n">
-        <v>91628</v>
+        <v>91630</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>136663265</v>
       </c>
       <c r="B8" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>136663297</v>
       </c>
       <c r="B9" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>136663259</v>
       </c>
       <c r="B10" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>136663254</v>
       </c>
       <c r="B11" t="n">
-        <v>102479</v>
+        <v>102485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>136663318</v>
       </c>
       <c r="B12" t="n">
-        <v>102479</v>
+        <v>102485</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>136663327</v>
       </c>
       <c r="B13" t="n">
-        <v>102479</v>
+        <v>102485</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>136663306</v>
       </c>
       <c r="B14" t="n">
-        <v>103928</v>
+        <v>103934</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>136663313</v>
       </c>
       <c r="B15" t="n">
-        <v>103928</v>
+        <v>103934</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>136663331</v>
       </c>
       <c r="B16" t="n">
-        <v>103928</v>
+        <v>103934</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>136663248</v>
       </c>
       <c r="B17" t="n">
-        <v>98369</v>
+        <v>98375</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>136663250</v>
       </c>
       <c r="B18" t="n">
-        <v>101465</v>
+        <v>101471</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>136663257</v>
       </c>
       <c r="B19" t="n">
-        <v>101465</v>
+        <v>101471</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>136663308</v>
       </c>
       <c r="B20" t="n">
-        <v>101465</v>
+        <v>101471</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>136663324</v>
       </c>
       <c r="B21" t="n">
-        <v>101465</v>
+        <v>101471</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>136663325</v>
       </c>
       <c r="B22" t="n">
-        <v>101465</v>
+        <v>101471</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>136663264</v>
       </c>
       <c r="B23" t="n">
-        <v>79664</v>
+        <v>79668</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 4226-2026 artfynd.xlsx
+++ b/artfynd/A 4226-2026 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>136663274</v>
       </c>
       <c r="B3" t="n">
-        <v>89340</v>
+        <v>89342</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>136663296</v>
       </c>
       <c r="B4" t="n">
-        <v>93439</v>
+        <v>93441</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136663269</v>
       </c>
       <c r="B5" t="n">
-        <v>91622</v>
+        <v>91624</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>136663273</v>
       </c>
       <c r="B6" t="n">
-        <v>91622</v>
+        <v>91624</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>136663272</v>
       </c>
       <c r="B7" t="n">
-        <v>91630</v>
+        <v>91632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>136663265</v>
       </c>
       <c r="B8" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>136663297</v>
       </c>
       <c r="B9" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>136663259</v>
       </c>
       <c r="B10" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>136663254</v>
       </c>
       <c r="B11" t="n">
-        <v>102485</v>
+        <v>102487</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>136663318</v>
       </c>
       <c r="B12" t="n">
-        <v>102485</v>
+        <v>102487</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>136663327</v>
       </c>
       <c r="B13" t="n">
-        <v>102485</v>
+        <v>102487</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>136663306</v>
       </c>
       <c r="B14" t="n">
-        <v>103934</v>
+        <v>103936</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>136663313</v>
       </c>
       <c r="B15" t="n">
-        <v>103934</v>
+        <v>103936</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>136663331</v>
       </c>
       <c r="B16" t="n">
-        <v>103934</v>
+        <v>103936</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>136663248</v>
       </c>
       <c r="B17" t="n">
-        <v>98375</v>
+        <v>98377</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>136663250</v>
       </c>
       <c r="B18" t="n">
-        <v>101471</v>
+        <v>101473</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>136663257</v>
       </c>
       <c r="B19" t="n">
-        <v>101471</v>
+        <v>101473</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>136663308</v>
       </c>
       <c r="B20" t="n">
-        <v>101471</v>
+        <v>101473</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>136663324</v>
       </c>
       <c r="B21" t="n">
-        <v>101471</v>
+        <v>101473</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>136663325</v>
       </c>
       <c r="B22" t="n">
-        <v>101471</v>
+        <v>101473</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>136663264</v>
       </c>
       <c r="B23" t="n">
-        <v>79668</v>
+        <v>79670</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 4226-2026 artfynd.xlsx
+++ b/artfynd/A 4226-2026 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>136663274</v>
       </c>
       <c r="B3" t="n">
-        <v>89342</v>
+        <v>89343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>136663296</v>
       </c>
       <c r="B4" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136663269</v>
       </c>
       <c r="B5" t="n">
-        <v>91624</v>
+        <v>91625</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>136663273</v>
       </c>
       <c r="B6" t="n">
-        <v>91624</v>
+        <v>91625</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>136663272</v>
       </c>
       <c r="B7" t="n">
-        <v>91632</v>
+        <v>91633</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>136663265</v>
       </c>
       <c r="B8" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>136663297</v>
       </c>
       <c r="B9" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>136663259</v>
       </c>
       <c r="B10" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>136663254</v>
       </c>
       <c r="B11" t="n">
-        <v>102487</v>
+        <v>102488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>136663318</v>
       </c>
       <c r="B12" t="n">
-        <v>102487</v>
+        <v>102488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>136663327</v>
       </c>
       <c r="B13" t="n">
-        <v>102487</v>
+        <v>102488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>136663306</v>
       </c>
       <c r="B14" t="n">
-        <v>103936</v>
+        <v>103937</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>136663313</v>
       </c>
       <c r="B15" t="n">
-        <v>103936</v>
+        <v>103937</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>136663331</v>
       </c>
       <c r="B16" t="n">
-        <v>103936</v>
+        <v>103937</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>136663248</v>
       </c>
       <c r="B17" t="n">
-        <v>98377</v>
+        <v>98378</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>136663250</v>
       </c>
       <c r="B18" t="n">
-        <v>101473</v>
+        <v>101474</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>136663257</v>
       </c>
       <c r="B19" t="n">
-        <v>101473</v>
+        <v>101474</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>136663308</v>
       </c>
       <c r="B20" t="n">
-        <v>101473</v>
+        <v>101474</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>136663324</v>
       </c>
       <c r="B21" t="n">
-        <v>101473</v>
+        <v>101474</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>136663325</v>
       </c>
       <c r="B22" t="n">
-        <v>101473</v>
+        <v>101474</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>136663264</v>
       </c>
       <c r="B23" t="n">
-        <v>79670</v>
+        <v>79671</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 4226-2026 artfynd.xlsx
+++ b/artfynd/A 4226-2026 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>136663274</v>
       </c>
       <c r="B3" t="n">
-        <v>89343</v>
+        <v>89349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>136663296</v>
       </c>
       <c r="B4" t="n">
-        <v>93442</v>
+        <v>93448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136663269</v>
       </c>
       <c r="B5" t="n">
-        <v>91625</v>
+        <v>91631</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>136663273</v>
       </c>
       <c r="B6" t="n">
-        <v>91625</v>
+        <v>91631</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>136663272</v>
       </c>
       <c r="B7" t="n">
-        <v>91633</v>
+        <v>91639</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>136663265</v>
       </c>
       <c r="B8" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>136663297</v>
       </c>
       <c r="B9" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>136663254</v>
       </c>
       <c r="B11" t="n">
-        <v>102488</v>
+        <v>102494</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>136663318</v>
       </c>
       <c r="B12" t="n">
-        <v>102488</v>
+        <v>102494</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>136663327</v>
       </c>
       <c r="B13" t="n">
-        <v>102488</v>
+        <v>102494</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>136663306</v>
       </c>
       <c r="B14" t="n">
-        <v>103937</v>
+        <v>103943</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>136663313</v>
       </c>
       <c r="B15" t="n">
-        <v>103937</v>
+        <v>103943</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>136663331</v>
       </c>
       <c r="B16" t="n">
-        <v>103937</v>
+        <v>103943</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>136663248</v>
       </c>
       <c r="B17" t="n">
-        <v>98378</v>
+        <v>98384</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>136663250</v>
       </c>
       <c r="B18" t="n">
-        <v>101474</v>
+        <v>101480</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>136663257</v>
       </c>
       <c r="B19" t="n">
-        <v>101474</v>
+        <v>101480</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>136663308</v>
       </c>
       <c r="B20" t="n">
-        <v>101474</v>
+        <v>101480</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>136663324</v>
       </c>
       <c r="B21" t="n">
-        <v>101474</v>
+        <v>101480</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>136663325</v>
       </c>
       <c r="B22" t="n">
-        <v>101474</v>
+        <v>101480</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 4226-2026 artfynd.xlsx
+++ b/artfynd/A 4226-2026 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>136663274</v>
       </c>
       <c r="B3" t="n">
-        <v>89349</v>
+        <v>89353</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>136663296</v>
       </c>
       <c r="B4" t="n">
-        <v>93448</v>
+        <v>93452</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136663269</v>
       </c>
       <c r="B5" t="n">
-        <v>91631</v>
+        <v>91635</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>136663273</v>
       </c>
       <c r="B6" t="n">
-        <v>91631</v>
+        <v>91635</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>136663272</v>
       </c>
       <c r="B7" t="n">
-        <v>91639</v>
+        <v>91643</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>136663265</v>
       </c>
       <c r="B8" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>136663297</v>
       </c>
       <c r="B9" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>136663259</v>
       </c>
       <c r="B10" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>136663254</v>
       </c>
       <c r="B11" t="n">
-        <v>102494</v>
+        <v>102498</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>136663318</v>
       </c>
       <c r="B12" t="n">
-        <v>102494</v>
+        <v>102498</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>136663327</v>
       </c>
       <c r="B13" t="n">
-        <v>102494</v>
+        <v>102498</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>136663306</v>
       </c>
       <c r="B14" t="n">
-        <v>103943</v>
+        <v>103947</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>136663313</v>
       </c>
       <c r="B15" t="n">
-        <v>103943</v>
+        <v>103947</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>136663331</v>
       </c>
       <c r="B16" t="n">
-        <v>103943</v>
+        <v>103947</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>136663248</v>
       </c>
       <c r="B17" t="n">
-        <v>98384</v>
+        <v>98388</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>136663250</v>
       </c>
       <c r="B18" t="n">
-        <v>101480</v>
+        <v>101484</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>136663257</v>
       </c>
       <c r="B19" t="n">
-        <v>101480</v>
+        <v>101484</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>136663308</v>
       </c>
       <c r="B20" t="n">
-        <v>101480</v>
+        <v>101484</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>136663324</v>
       </c>
       <c r="B21" t="n">
-        <v>101480</v>
+        <v>101484</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>136663325</v>
       </c>
       <c r="B22" t="n">
-        <v>101480</v>
+        <v>101484</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>136663264</v>
       </c>
       <c r="B23" t="n">
-        <v>79671</v>
+        <v>79673</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 4226-2026 artfynd.xlsx
+++ b/artfynd/A 4226-2026 artfynd.xlsx
@@ -1660,7 +1660,7 @@
         <v>136663254</v>
       </c>
       <c r="B11" t="n">
-        <v>102498</v>
+        <v>102500</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>136663318</v>
       </c>
       <c r="B12" t="n">
-        <v>102498</v>
+        <v>102500</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>136663327</v>
       </c>
       <c r="B13" t="n">
-        <v>102498</v>
+        <v>102500</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>136663306</v>
       </c>
       <c r="B14" t="n">
-        <v>103947</v>
+        <v>103949</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>136663313</v>
       </c>
       <c r="B15" t="n">
-        <v>103947</v>
+        <v>103949</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>136663331</v>
       </c>
       <c r="B16" t="n">
-        <v>103947</v>
+        <v>103949</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>136663248</v>
       </c>
       <c r="B17" t="n">
-        <v>98388</v>
+        <v>98390</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>136663250</v>
       </c>
       <c r="B18" t="n">
-        <v>101484</v>
+        <v>101486</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>136663257</v>
       </c>
       <c r="B19" t="n">
-        <v>101484</v>
+        <v>101486</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>136663308</v>
       </c>
       <c r="B20" t="n">
-        <v>101484</v>
+        <v>101486</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>136663324</v>
       </c>
       <c r="B21" t="n">
-        <v>101484</v>
+        <v>101486</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>136663325</v>
       </c>
       <c r="B22" t="n">
-        <v>101484</v>
+        <v>101486</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 4226-2026 artfynd.xlsx
+++ b/artfynd/A 4226-2026 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>136663274</v>
       </c>
       <c r="B3" t="n">
-        <v>89353</v>
+        <v>89355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>136663296</v>
       </c>
       <c r="B4" t="n">
-        <v>93452</v>
+        <v>93454</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136663269</v>
       </c>
       <c r="B5" t="n">
-        <v>91635</v>
+        <v>91637</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>136663273</v>
       </c>
       <c r="B6" t="n">
-        <v>91635</v>
+        <v>91637</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>136663272</v>
       </c>
       <c r="B7" t="n">
-        <v>91643</v>
+        <v>91645</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>136663265</v>
       </c>
       <c r="B8" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>136663297</v>
       </c>
       <c r="B9" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>136663259</v>
       </c>
       <c r="B10" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>136663254</v>
       </c>
       <c r="B11" t="n">
-        <v>102500</v>
+        <v>102502</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>136663318</v>
       </c>
       <c r="B12" t="n">
-        <v>102500</v>
+        <v>102502</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>136663327</v>
       </c>
       <c r="B13" t="n">
-        <v>102500</v>
+        <v>102502</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>136663306</v>
       </c>
       <c r="B14" t="n">
-        <v>103949</v>
+        <v>103951</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>136663313</v>
       </c>
       <c r="B15" t="n">
-        <v>103949</v>
+        <v>103951</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>136663331</v>
       </c>
       <c r="B16" t="n">
-        <v>103949</v>
+        <v>103951</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>136663248</v>
       </c>
       <c r="B17" t="n">
-        <v>98390</v>
+        <v>98392</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>136663250</v>
       </c>
       <c r="B18" t="n">
-        <v>101486</v>
+        <v>101488</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>136663257</v>
       </c>
       <c r="B19" t="n">
-        <v>101486</v>
+        <v>101488</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>136663308</v>
       </c>
       <c r="B20" t="n">
-        <v>101486</v>
+        <v>101488</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>136663324</v>
       </c>
       <c r="B21" t="n">
-        <v>101486</v>
+        <v>101488</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>136663325</v>
       </c>
       <c r="B22" t="n">
-        <v>101486</v>
+        <v>101488</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>136663264</v>
       </c>
       <c r="B23" t="n">
-        <v>79673</v>
+        <v>79676</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 4226-2026 artfynd.xlsx
+++ b/artfynd/A 4226-2026 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>136663274</v>
       </c>
       <c r="B3" t="n">
-        <v>89355</v>
+        <v>89368</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>136663296</v>
       </c>
       <c r="B4" t="n">
-        <v>93454</v>
+        <v>93467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136663269</v>
       </c>
       <c r="B5" t="n">
-        <v>91637</v>
+        <v>91650</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>136663273</v>
       </c>
       <c r="B6" t="n">
-        <v>91637</v>
+        <v>91650</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>136663272</v>
       </c>
       <c r="B7" t="n">
-        <v>91645</v>
+        <v>91658</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>136663265</v>
       </c>
       <c r="B8" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>136663297</v>
       </c>
       <c r="B9" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>136663259</v>
       </c>
       <c r="B10" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>136663254</v>
       </c>
       <c r="B11" t="n">
-        <v>102502</v>
+        <v>102515</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>136663318</v>
       </c>
       <c r="B12" t="n">
-        <v>102502</v>
+        <v>102515</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>136663327</v>
       </c>
       <c r="B13" t="n">
-        <v>102502</v>
+        <v>102515</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>136663306</v>
       </c>
       <c r="B14" t="n">
-        <v>103951</v>
+        <v>103964</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>136663313</v>
       </c>
       <c r="B15" t="n">
-        <v>103951</v>
+        <v>103964</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>136663331</v>
       </c>
       <c r="B16" t="n">
-        <v>103951</v>
+        <v>103964</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>136663248</v>
       </c>
       <c r="B17" t="n">
-        <v>98392</v>
+        <v>98405</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>136663250</v>
       </c>
       <c r="B18" t="n">
-        <v>101488</v>
+        <v>101501</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>136663257</v>
       </c>
       <c r="B19" t="n">
-        <v>101488</v>
+        <v>101501</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>136663308</v>
       </c>
       <c r="B20" t="n">
-        <v>101488</v>
+        <v>101501</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>136663324</v>
       </c>
       <c r="B21" t="n">
-        <v>101488</v>
+        <v>101501</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>136663325</v>
       </c>
       <c r="B22" t="n">
-        <v>101488</v>
+        <v>101501</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>136663264</v>
       </c>
       <c r="B23" t="n">
-        <v>79676</v>
+        <v>79689</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 4226-2026 artfynd.xlsx
+++ b/artfynd/A 4226-2026 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>136663274</v>
       </c>
       <c r="B3" t="n">
-        <v>89368</v>
+        <v>89370</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>136663296</v>
       </c>
       <c r="B4" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136663269</v>
       </c>
       <c r="B5" t="n">
-        <v>91650</v>
+        <v>91652</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>136663273</v>
       </c>
       <c r="B6" t="n">
-        <v>91650</v>
+        <v>91652</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>136663272</v>
       </c>
       <c r="B7" t="n">
-        <v>91658</v>
+        <v>91660</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>136663265</v>
       </c>
       <c r="B8" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>136663297</v>
       </c>
       <c r="B9" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>136663259</v>
       </c>
       <c r="B10" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>136663254</v>
       </c>
       <c r="B11" t="n">
-        <v>102515</v>
+        <v>102517</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>136663318</v>
       </c>
       <c r="B12" t="n">
-        <v>102515</v>
+        <v>102517</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>136663327</v>
       </c>
       <c r="B13" t="n">
-        <v>102515</v>
+        <v>102517</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>136663306</v>
       </c>
       <c r="B14" t="n">
-        <v>103964</v>
+        <v>103966</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>136663313</v>
       </c>
       <c r="B15" t="n">
-        <v>103964</v>
+        <v>103966</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>136663331</v>
       </c>
       <c r="B16" t="n">
-        <v>103964</v>
+        <v>103966</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>136663248</v>
       </c>
       <c r="B17" t="n">
-        <v>98405</v>
+        <v>98407</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>136663250</v>
       </c>
       <c r="B18" t="n">
-        <v>101501</v>
+        <v>101503</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>136663257</v>
       </c>
       <c r="B19" t="n">
-        <v>101501</v>
+        <v>101503</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>136663308</v>
       </c>
       <c r="B20" t="n">
-        <v>101501</v>
+        <v>101503</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>136663324</v>
       </c>
       <c r="B21" t="n">
-        <v>101501</v>
+        <v>101503</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>136663325</v>
       </c>
       <c r="B22" t="n">
-        <v>101501</v>
+        <v>101503</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>136663264</v>
       </c>
       <c r="B23" t="n">
-        <v>79689</v>
+        <v>79691</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 4226-2026 artfynd.xlsx
+++ b/artfynd/A 4226-2026 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>136663274</v>
       </c>
       <c r="B3" t="n">
-        <v>89370</v>
+        <v>89373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>136663296</v>
       </c>
       <c r="B4" t="n">
-        <v>93468</v>
+        <v>93471</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136663269</v>
       </c>
       <c r="B5" t="n">
-        <v>91652</v>
+        <v>91655</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>136663273</v>
       </c>
       <c r="B6" t="n">
-        <v>91652</v>
+        <v>91655</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>136663272</v>
       </c>
       <c r="B7" t="n">
-        <v>91660</v>
+        <v>91663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>136663265</v>
       </c>
       <c r="B8" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>136663297</v>
       </c>
       <c r="B9" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>136663254</v>
       </c>
       <c r="B11" t="n">
-        <v>102517</v>
+        <v>102520</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>136663318</v>
       </c>
       <c r="B12" t="n">
-        <v>102517</v>
+        <v>102520</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>136663327</v>
       </c>
       <c r="B13" t="n">
-        <v>102517</v>
+        <v>102520</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>136663306</v>
       </c>
       <c r="B14" t="n">
-        <v>103966</v>
+        <v>103969</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>136663313</v>
       </c>
       <c r="B15" t="n">
-        <v>103966</v>
+        <v>103969</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>136663331</v>
       </c>
       <c r="B16" t="n">
-        <v>103966</v>
+        <v>103969</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>136663248</v>
       </c>
       <c r="B17" t="n">
-        <v>98407</v>
+        <v>98410</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>136663250</v>
       </c>
       <c r="B18" t="n">
-        <v>101503</v>
+        <v>101506</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>136663257</v>
       </c>
       <c r="B19" t="n">
-        <v>101503</v>
+        <v>101506</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>136663308</v>
       </c>
       <c r="B20" t="n">
-        <v>101503</v>
+        <v>101506</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>136663324</v>
       </c>
       <c r="B21" t="n">
-        <v>101503</v>
+        <v>101506</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>136663325</v>
       </c>
       <c r="B22" t="n">
-        <v>101503</v>
+        <v>101506</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
